--- a/詩經/分類.xlsx
+++ b/詩經/分類.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\ShijingNature\shijing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\ShijingNature\詩經\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63AF2FD-6BC7-4685-BCAB-1BFC161C00C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34496DF-DA09-4808-9743-F7AA8085F3C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -1064,10 +1064,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>其他</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>昆蟲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1210,6 +1206,10 @@
   </si>
   <si>
     <t>社會政治</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兩棲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1579,10 +1579,10 @@
         <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1593,7 +1593,7 @@
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1610,7 +1610,7 @@
         <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1621,7 +1621,7 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1632,10 +1632,10 @@
         <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1646,7 +1646,7 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1660,7 +1660,7 @@
         <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1674,10 +1674,10 @@
         <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1691,7 +1691,7 @@
         <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1702,10 +1702,10 @@
         <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1716,10 +1716,10 @@
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1727,10 +1727,10 @@
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1741,13 +1741,13 @@
         <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>263</v>
+        <v>304</v>
       </c>
       <c r="G13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1761,7 +1761,7 @@
         <v>141</v>
       </c>
       <c r="H14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1769,7 +1769,7 @@
         <v>125</v>
       </c>
       <c r="H15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1780,10 +1780,10 @@
         <v>107</v>
       </c>
       <c r="G16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.25">
@@ -1860,10 +1860,10 @@
         <v>182</v>
       </c>
       <c r="E1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1" t="s">
         <v>12</v>
@@ -1880,10 +1880,10 @@
         <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
@@ -1900,10 +1900,10 @@
         <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H3" t="s">
         <v>12</v>
@@ -1920,10 +1920,10 @@
         <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H4" t="s">
         <v>12</v>
@@ -1940,10 +1940,10 @@
         <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H5" t="s">
         <v>12</v>
@@ -1960,10 +1960,10 @@
         <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H6" t="s">
         <v>12</v>
@@ -1980,10 +1980,10 @@
         <v>190</v>
       </c>
       <c r="E7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H7" t="s">
         <v>12</v>
@@ -2000,7 +2000,7 @@
         <v>190</v>
       </c>
       <c r="E8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -2020,10 +2020,10 @@
         <v>182</v>
       </c>
       <c r="E9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H9" t="s">
         <v>12</v>
@@ -2040,10 +2040,10 @@
         <v>183</v>
       </c>
       <c r="E10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
@@ -2060,10 +2060,10 @@
         <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H11" t="s">
         <v>12</v>
@@ -2080,10 +2080,10 @@
         <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H12" t="s">
         <v>62</v>
@@ -2100,7 +2100,7 @@
         <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -2120,10 +2120,10 @@
         <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H14" t="s">
         <v>62</v>
@@ -2140,7 +2140,7 @@
         <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F15" t="s">
         <v>34</v>
@@ -2160,10 +2160,10 @@
         <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H16" t="s">
         <v>62</v>
@@ -2180,10 +2180,10 @@
         <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H17" t="s">
         <v>62</v>
@@ -2200,10 +2200,10 @@
         <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H18" t="s">
         <v>62</v>
@@ -2220,10 +2220,10 @@
         <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H19" t="s">
         <v>62</v>
@@ -2240,10 +2240,10 @@
         <v>183</v>
       </c>
       <c r="E20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H20" t="s">
         <v>62</v>
@@ -2260,10 +2260,10 @@
         <v>94</v>
       </c>
       <c r="E21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H21" t="s">
         <v>62</v>
@@ -2280,10 +2280,10 @@
         <v>183</v>
       </c>
       <c r="E22" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F22" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H22" t="s">
         <v>62</v>
@@ -2300,10 +2300,10 @@
         <v>182</v>
       </c>
       <c r="E23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H23" t="s">
         <v>62</v>
@@ -2320,10 +2320,10 @@
         <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F24" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H24" t="s">
         <v>62</v>
@@ -2340,10 +2340,10 @@
         <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F25" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H25" t="s">
         <v>62</v>
@@ -2360,10 +2360,10 @@
         <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H26" t="s">
         <v>79</v>
@@ -2380,10 +2380,10 @@
         <v>96</v>
       </c>
       <c r="E27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H27" t="s">
         <v>79</v>
@@ -2400,10 +2400,10 @@
         <v>98</v>
       </c>
       <c r="E28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F28" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H28" t="s">
         <v>79</v>
@@ -2420,10 +2420,10 @@
         <v>96</v>
       </c>
       <c r="E29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H29" t="s">
         <v>79</v>
@@ -2440,10 +2440,10 @@
         <v>96</v>
       </c>
       <c r="E30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H30" t="s">
         <v>79</v>
@@ -2460,10 +2460,10 @@
         <v>99</v>
       </c>
       <c r="E31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H31" t="s">
         <v>79</v>
@@ -2480,10 +2480,10 @@
         <v>101</v>
       </c>
       <c r="E32" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H32" t="s">
         <v>79</v>
@@ -2500,10 +2500,10 @@
         <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H33" t="s">
         <v>79</v>
@@ -2520,10 +2520,10 @@
         <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H34" t="s">
         <v>79</v>
@@ -2540,10 +2540,10 @@
         <v>105</v>
       </c>
       <c r="E35" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F35" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H35" t="s">
         <v>79</v>
@@ -2560,10 +2560,10 @@
         <v>105</v>
       </c>
       <c r="E36" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F36" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H36" t="s">
         <v>79</v>
@@ -2580,10 +2580,10 @@
         <v>92</v>
       </c>
       <c r="E37" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F37" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H37" t="s">
         <v>79</v>
@@ -2600,10 +2600,10 @@
         <v>182</v>
       </c>
       <c r="E38" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F38" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H38" t="s">
         <v>79</v>
@@ -2620,10 +2620,10 @@
         <v>99</v>
       </c>
       <c r="E39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H39" t="s">
         <v>79</v>
@@ -2640,10 +2640,10 @@
         <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F40" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H40" t="s">
         <v>79</v>
@@ -2660,10 +2660,10 @@
         <v>92</v>
       </c>
       <c r="E41" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H41" t="s">
         <v>79</v>
@@ -2680,10 +2680,10 @@
         <v>182</v>
       </c>
       <c r="E42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H42" t="s">
         <v>79</v>
@@ -2700,10 +2700,10 @@
         <v>92</v>
       </c>
       <c r="E43" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F43" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H43" t="s">
         <v>79</v>
@@ -2720,10 +2720,10 @@
         <v>98</v>
       </c>
       <c r="E44" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F44" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H44" t="s">
         <v>79</v>
@@ -2740,10 +2740,10 @@
         <v>183</v>
       </c>
       <c r="E45" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H45" t="s">
         <v>117</v>
@@ -2760,10 +2760,10 @@
         <v>92</v>
       </c>
       <c r="E46" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F46" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H46" t="s">
         <v>117</v>
@@ -2780,10 +2780,10 @@
         <v>92</v>
       </c>
       <c r="E47" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F47" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H47" t="s">
         <v>117</v>
@@ -2800,10 +2800,10 @@
         <v>182</v>
       </c>
       <c r="E48" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H48" t="s">
         <v>117</v>
@@ -2820,10 +2820,10 @@
         <v>92</v>
       </c>
       <c r="E49" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F49" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H49" t="s">
         <v>117</v>
@@ -2840,10 +2840,10 @@
         <v>90</v>
       </c>
       <c r="E50" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F50" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H50" t="s">
         <v>117</v>
@@ -2860,10 +2860,10 @@
         <v>92</v>
       </c>
       <c r="E51" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F51" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H51" t="s">
         <v>117</v>
@@ -2880,10 +2880,10 @@
         <v>92</v>
       </c>
       <c r="E52" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F52" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H52" t="s">
         <v>117</v>
@@ -2900,10 +2900,10 @@
         <v>182</v>
       </c>
       <c r="E53" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F53" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H53" t="s">
         <v>117</v>
@@ -2920,10 +2920,10 @@
         <v>99</v>
       </c>
       <c r="E54" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F54" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H54" t="s">
         <v>117</v>
@@ -2940,10 +2940,10 @@
         <v>90</v>
       </c>
       <c r="E55" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F55" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H55" t="s">
         <v>145</v>
@@ -2960,10 +2960,10 @@
         <v>90</v>
       </c>
       <c r="E56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F56" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H56" t="s">
         <v>145</v>
@@ -2980,10 +2980,10 @@
         <v>37</v>
       </c>
       <c r="E57" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F57" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H57" t="s">
         <v>145</v>
@@ -3000,10 +3000,10 @@
         <v>96</v>
       </c>
       <c r="E58" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F58" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H58" t="s">
         <v>145</v>
@@ -3020,10 +3020,10 @@
         <v>183</v>
       </c>
       <c r="E59" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F59" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H59" t="s">
         <v>145</v>
@@ -3040,10 +3040,10 @@
         <v>92</v>
       </c>
       <c r="E60" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F60" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H60" t="s">
         <v>145</v>
@@ -3060,10 +3060,10 @@
         <v>99</v>
       </c>
       <c r="E61" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F61" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H61" t="s">
         <v>145</v>
@@ -3080,10 +3080,10 @@
         <v>39</v>
       </c>
       <c r="E62" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F62" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H62" t="s">
         <v>145</v>
@@ -3100,10 +3100,10 @@
         <v>39</v>
       </c>
       <c r="E63" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F63" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H63" t="s">
         <v>145</v>
@@ -3120,10 +3120,10 @@
         <v>182</v>
       </c>
       <c r="E64" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F64" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H64" t="s">
         <v>145</v>
@@ -3140,10 +3140,10 @@
         <v>92</v>
       </c>
       <c r="E65" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F65" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H65" t="s">
         <v>146</v>
@@ -3160,10 +3160,10 @@
         <v>39</v>
       </c>
       <c r="E66" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F66" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H66" t="s">
         <v>146</v>
@@ -3180,10 +3180,10 @@
         <v>159</v>
       </c>
       <c r="E67" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F67" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H67" t="s">
         <v>146</v>
@@ -3200,10 +3200,10 @@
         <v>99</v>
       </c>
       <c r="E68" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F68" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H68" t="s">
         <v>146</v>
@@ -3220,10 +3220,10 @@
         <v>96</v>
       </c>
       <c r="E69" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F69" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H69" t="s">
         <v>146</v>
@@ -3240,10 +3240,10 @@
         <v>92</v>
       </c>
       <c r="E70" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F70" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H70" t="s">
         <v>146</v>
@@ -3260,10 +3260,10 @@
         <v>99</v>
       </c>
       <c r="E71" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F71" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H71" t="s">
         <v>146</v>
@@ -3280,10 +3280,10 @@
         <v>183</v>
       </c>
       <c r="E72" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H72" t="s">
         <v>146</v>
@@ -3300,10 +3300,10 @@
         <v>96</v>
       </c>
       <c r="E73" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F73" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H73" t="s">
         <v>146</v>
@@ -3320,10 +3320,10 @@
         <v>182</v>
       </c>
       <c r="E74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H74" t="s">
         <v>146</v>
@@ -3340,10 +3340,10 @@
         <v>101</v>
       </c>
       <c r="E75" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F75" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H75" t="s">
         <v>154</v>
@@ -3360,10 +3360,10 @@
         <v>182</v>
       </c>
       <c r="E76" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F76" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H76" t="s">
         <v>154</v>
@@ -3380,10 +3380,10 @@
         <v>182</v>
       </c>
       <c r="E77" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F77" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H77" t="s">
         <v>154</v>
@@ -3400,10 +3400,10 @@
         <v>182</v>
       </c>
       <c r="E78" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F78" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H78" t="s">
         <v>154</v>
@@ -3420,10 +3420,10 @@
         <v>92</v>
       </c>
       <c r="E79" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F79" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H79" t="s">
         <v>154</v>
@@ -3440,10 +3440,10 @@
         <v>90</v>
       </c>
       <c r="E80" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H80" t="s">
         <v>154</v>
@@ -3460,10 +3460,10 @@
         <v>187</v>
       </c>
       <c r="E81" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F81" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H81" t="s">
         <v>154</v>
@@ -3480,10 +3480,10 @@
         <v>101</v>
       </c>
       <c r="E82" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F82" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H82" t="s">
         <v>154</v>
@@ -3500,10 +3500,10 @@
         <v>182</v>
       </c>
       <c r="E83" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F83" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H83" t="s">
         <v>154</v>
@@ -3520,10 +3520,10 @@
         <v>182</v>
       </c>
       <c r="E84" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F84" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H84" t="s">
         <v>154</v>
@@ -3534,10 +3534,10 @@
         <v>166</v>
       </c>
       <c r="E85" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F85" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H85" t="s">
         <v>154</v>
@@ -3554,10 +3554,10 @@
         <v>187</v>
       </c>
       <c r="E86" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F86" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H86" t="s">
         <v>154</v>
@@ -3574,10 +3574,10 @@
         <v>187</v>
       </c>
       <c r="E87" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H87" t="s">
         <v>154</v>
@@ -3594,10 +3594,10 @@
         <v>182</v>
       </c>
       <c r="E88" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F88" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H88" t="s">
         <v>154</v>
@@ -3614,10 +3614,10 @@
         <v>182</v>
       </c>
       <c r="E89" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F89" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H89" t="s">
         <v>154</v>
@@ -3634,10 +3634,10 @@
         <v>182</v>
       </c>
       <c r="E90" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F90" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H90" t="s">
         <v>154</v>
@@ -3654,10 +3654,10 @@
         <v>182</v>
       </c>
       <c r="E91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F91" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H91" t="s">
         <v>154</v>
@@ -3674,10 +3674,10 @@
         <v>101</v>
       </c>
       <c r="E92" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F92" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H92" t="s">
         <v>154</v>
@@ -3694,10 +3694,10 @@
         <v>182</v>
       </c>
       <c r="E93" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F93" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H93" t="s">
         <v>154</v>
@@ -3714,10 +3714,10 @@
         <v>182</v>
       </c>
       <c r="E94" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F94" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H94" t="s">
         <v>154</v>
@@ -3734,10 +3734,10 @@
         <v>182</v>
       </c>
       <c r="E95" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F95" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H95" t="s">
         <v>154</v>
@@ -3754,10 +3754,10 @@
         <v>101</v>
       </c>
       <c r="E96" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F96" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H96" t="s">
         <v>177</v>
@@ -3774,10 +3774,10 @@
         <v>190</v>
       </c>
       <c r="E97" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F97" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H97" t="s">
         <v>177</v>
@@ -3794,10 +3794,10 @@
         <v>37</v>
       </c>
       <c r="E98" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F98" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H98" t="s">
         <v>177</v>
@@ -3814,10 +3814,10 @@
         <v>191</v>
       </c>
       <c r="E99" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F99" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H99" t="s">
         <v>177</v>
@@ -3834,10 +3834,10 @@
         <v>92</v>
       </c>
       <c r="E100" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F100" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H100" t="s">
         <v>177</v>
@@ -3854,10 +3854,10 @@
         <v>92</v>
       </c>
       <c r="E101" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F101" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H101" t="s">
         <v>177</v>
@@ -3874,10 +3874,10 @@
         <v>39</v>
       </c>
       <c r="E102" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F102" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H102" t="s">
         <v>177</v>
@@ -3894,10 +3894,10 @@
         <v>90</v>
       </c>
       <c r="E103" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F103" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H103" t="s">
         <v>177</v>
@@ -3914,10 +3914,10 @@
         <v>37</v>
       </c>
       <c r="E104" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F104" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H104" t="s">
         <v>177</v>
@@ -3934,10 +3934,10 @@
         <v>92</v>
       </c>
       <c r="E105" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F105" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H105" t="s">
         <v>177</v>
@@ -3954,10 +3954,10 @@
         <v>90</v>
       </c>
       <c r="E106" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F106" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H106" t="s">
         <v>177</v>
@@ -3974,10 +3974,10 @@
         <v>92</v>
       </c>
       <c r="E107" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F107" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H107" t="s">
         <v>199</v>
@@ -3994,10 +3994,10 @@
         <v>92</v>
       </c>
       <c r="E108" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F108" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H108" t="s">
         <v>199</v>
@@ -4014,10 +4014,10 @@
         <v>92</v>
       </c>
       <c r="E109" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F109" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H109" t="s">
         <v>199</v>
@@ -4034,10 +4034,10 @@
         <v>98</v>
       </c>
       <c r="E110" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F110" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H110" t="s">
         <v>199</v>
@@ -4054,10 +4054,10 @@
         <v>204</v>
       </c>
       <c r="E111" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F111" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H111" t="s">
         <v>199</v>
@@ -4074,10 +4074,10 @@
         <v>92</v>
       </c>
       <c r="E112" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F112" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H112" t="s">
         <v>199</v>
@@ -4094,10 +4094,10 @@
         <v>92</v>
       </c>
       <c r="E113" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F113" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H113" t="s">
         <v>199</v>
@@ -4114,10 +4114,10 @@
         <v>90</v>
       </c>
       <c r="E114" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F114" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H114" t="s">
         <v>208</v>
@@ -4134,10 +4134,10 @@
         <v>159</v>
       </c>
       <c r="E115" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F115" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H115" t="s">
         <v>208</v>
@@ -4154,10 +4154,10 @@
         <v>37</v>
       </c>
       <c r="E116" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F116" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H116" t="s">
         <v>208</v>
@@ -4174,10 +4174,10 @@
         <v>101</v>
       </c>
       <c r="E117" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H117" t="s">
         <v>208</v>
@@ -4194,10 +4194,10 @@
         <v>37</v>
       </c>
       <c r="E118" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H118" t="s">
         <v>208</v>
@@ -4214,10 +4214,10 @@
         <v>101</v>
       </c>
       <c r="E119" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F119" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H119" t="s">
         <v>208</v>
@@ -4234,10 +4234,10 @@
         <v>92</v>
       </c>
       <c r="E120" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F120" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H120" t="s">
         <v>208</v>
@@ -4254,10 +4254,10 @@
         <v>101</v>
       </c>
       <c r="E121" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H121" t="s">
         <v>208</v>
@@ -4268,10 +4268,10 @@
         <v>216</v>
       </c>
       <c r="E122" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F122" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H122" t="s">
         <v>208</v>
@@ -4282,10 +4282,10 @@
         <v>217</v>
       </c>
       <c r="E123" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H123" t="s">
         <v>208</v>
@@ -4302,10 +4302,10 @@
         <v>96</v>
       </c>
       <c r="E124" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F124" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H124" t="s">
         <v>208</v>
@@ -4322,10 +4322,10 @@
         <v>92</v>
       </c>
       <c r="E125" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H125" t="s">
         <v>208</v>
@@ -4342,10 +4342,10 @@
         <v>90</v>
       </c>
       <c r="E126" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F126" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H126" t="s">
         <v>221</v>
@@ -4362,10 +4362,10 @@
         <v>90</v>
       </c>
       <c r="E127" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F127" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H127" t="s">
         <v>221</v>
@@ -4382,10 +4382,10 @@
         <v>39</v>
       </c>
       <c r="E128" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H128" t="s">
         <v>221</v>
@@ -4402,10 +4402,10 @@
         <v>187</v>
       </c>
       <c r="E129" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F129" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H129" t="s">
         <v>221</v>
@@ -4422,10 +4422,10 @@
         <v>90</v>
       </c>
       <c r="E130" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F130" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H130" t="s">
         <v>221</v>
@@ -4442,10 +4442,10 @@
         <v>92</v>
       </c>
       <c r="E131" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F131" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H131" t="s">
         <v>221</v>
@@ -4462,10 +4462,10 @@
         <v>39</v>
       </c>
       <c r="E132" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F132" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H132" t="s">
         <v>221</v>
@@ -4476,10 +4476,10 @@
         <v>216</v>
       </c>
       <c r="E133" t="s">
+        <v>283</v>
+      </c>
+      <c r="F133" t="s">
         <v>284</v>
-      </c>
-      <c r="F133" t="s">
-        <v>285</v>
       </c>
       <c r="H133" t="s">
         <v>221</v>
@@ -4496,10 +4496,10 @@
         <v>98</v>
       </c>
       <c r="E134" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F134" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H134" t="s">
         <v>221</v>
@@ -4516,10 +4516,10 @@
         <v>50</v>
       </c>
       <c r="E135" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F135" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H135" t="s">
         <v>221</v>
@@ -4536,10 +4536,10 @@
         <v>92</v>
       </c>
       <c r="E136" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F136" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H136" t="s">
         <v>231</v>
@@ -4556,10 +4556,10 @@
         <v>92</v>
       </c>
       <c r="E137" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F137" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H137" t="s">
         <v>231</v>
@@ -4570,10 +4570,10 @@
         <v>233</v>
       </c>
       <c r="E138" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F138" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H138" t="s">
         <v>231</v>
@@ -4590,10 +4590,10 @@
         <v>242</v>
       </c>
       <c r="E139" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F139" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H139" t="s">
         <v>231</v>
@@ -4610,10 +4610,10 @@
         <v>243</v>
       </c>
       <c r="E140" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F140" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H140" t="s">
         <v>231</v>
@@ -4630,10 +4630,10 @@
         <v>92</v>
       </c>
       <c r="E141" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F141" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H141" t="s">
         <v>231</v>
@@ -4650,10 +4650,10 @@
         <v>243</v>
       </c>
       <c r="E142" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F142" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H142" t="s">
         <v>231</v>
@@ -4670,10 +4670,10 @@
         <v>242</v>
       </c>
       <c r="E143" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F143" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H143" t="s">
         <v>231</v>
@@ -4690,10 +4690,10 @@
         <v>92</v>
       </c>
       <c r="E144" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F144" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H144" t="s">
         <v>231</v>
@@ -4710,10 +4710,10 @@
         <v>243</v>
       </c>
       <c r="E145" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F145" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H145" t="s">
         <v>231</v>
@@ -4730,10 +4730,10 @@
         <v>92</v>
       </c>
       <c r="E146" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F146" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H146" t="s">
         <v>245</v>
@@ -4750,10 +4750,10 @@
         <v>39</v>
       </c>
       <c r="E147" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F147" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H147" t="s">
         <v>245</v>
@@ -4764,10 +4764,10 @@
         <v>247</v>
       </c>
       <c r="E148" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F148" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H148" t="s">
         <v>245</v>
@@ -4784,10 +4784,10 @@
         <v>99</v>
       </c>
       <c r="E149" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F149" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H149" t="s">
         <v>245</v>
@@ -4804,10 +4804,10 @@
         <v>92</v>
       </c>
       <c r="E150" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F150" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H150" t="s">
         <v>249</v>
@@ -4824,10 +4824,10 @@
         <v>92</v>
       </c>
       <c r="E151" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F151" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H151" t="s">
         <v>249</v>
@@ -4844,10 +4844,10 @@
         <v>90</v>
       </c>
       <c r="E152" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F152" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H152" t="s">
         <v>249</v>
@@ -4864,10 +4864,10 @@
         <v>90</v>
       </c>
       <c r="E153" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F153" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H153" t="s">
         <v>249</v>
@@ -4884,10 +4884,10 @@
         <v>256</v>
       </c>
       <c r="E154" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F154" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H154" t="s">
         <v>254</v>
@@ -4904,10 +4904,10 @@
         <v>90</v>
       </c>
       <c r="E155" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H155" t="s">
         <v>254</v>
@@ -4924,10 +4924,10 @@
         <v>90</v>
       </c>
       <c r="E156" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F156" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H156" t="s">
         <v>254</v>
@@ -4938,10 +4938,10 @@
         <v>259</v>
       </c>
       <c r="E157" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F157" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H157" t="s">
         <v>254</v>
@@ -4958,10 +4958,10 @@
         <v>37</v>
       </c>
       <c r="E158" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H158" t="s">
         <v>254</v>
@@ -4978,10 +4978,10 @@
         <v>98</v>
       </c>
       <c r="E159" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F159" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H159" t="s">
         <v>254</v>
@@ -4998,10 +4998,10 @@
         <v>90</v>
       </c>
       <c r="E160" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F160" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H160" t="s">
         <v>254</v>
